--- a/mineru/model/xlsx/test_xlsx/xlsx_01.xlsx
+++ b/mineru/model/xlsx/test_xlsx/xlsx_01.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bytedance/rag/opensource/docling/tests/data/xlsx/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24F23DF9-99BA-744A-982A-14EFF12372E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="2" xr2:uid="{7BFEBC09-E794-024E-92A5-4E4755531B02}"/>
+    <workbookView windowHeight="16905"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,11 +12,8 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -38,8 +29,59 @@
 </workbook>
 </file>
 
+<file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="ID_EEE2D862C4E9461295D42240896EFDB1" descr="截图 2026-01-14 15-36-42"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="10058400" cy="5272405"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="ID_D0725FD5BF544D4B9C79E66BEBA01A89" descr="20250807-172515"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="7265670" cy="10058400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+</etc:cellImages>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="10">
   <si>
     <t xml:space="preserve">first </t>
   </si>
@@ -65,45 +107,401 @@
     <t>header</t>
   </si>
   <si>
-    <t>header (f)</t>
-  </si>
-  <si>
     <t>first (f)</t>
   </si>
   <si>
-    <t>header</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>header (f)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -111,34 +509,323 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
@@ -158,7 +845,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr lang="zh-CN" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -174,9 +861,11 @@
               <a:rPr lang="en-US"/>
               <a:t>'col-2', 'col-3', 'col-4' by 'col-1'</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -185,32 +874,12 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="zh-CN"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
       <c:layout/>
       <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
+        <c:scatterStyle val="marker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -249,6 +918,9 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet2!$A$2:$A$9</c:f>
@@ -316,11 +988,6 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-938B-B94B-A507-6AF67C8AC3DB}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -359,6 +1026,9 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet2!$A$2:$A$9</c:f>
@@ -426,11 +1096,6 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-938B-B94B-A507-6AF67C8AC3DB}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -469,6 +1134,9 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
           <c:xVal>
             <c:numRef>
               <c:f>Sheet2!$A$2:$A$9</c:f>
@@ -536,11 +1204,6 @@
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-938B-B94B-A507-6AF67C8AC3DB}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -581,7 +1244,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -597,9 +1260,11 @@
                   <a:rPr lang="en-US"/>
                   <a:t>col-1</a:t>
                 </a:r>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -608,26 +1273,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="zh-CN"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -651,7 +1296,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -663,7 +1308,6 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="309818255"/>
@@ -713,7 +1357,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -725,7 +1369,6 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="1284139040"/>
@@ -742,6 +1385,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -755,7 +1399,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -767,19 +1411,11 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="zh-CN"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
@@ -802,9 +1438,8 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr lang="zh-CN"/>
       </a:pPr>
-      <a:endParaRPr lang="zh-CN"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -816,7 +1451,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="zh-CN"/>
   <c:roundedCorners val="0"/>
@@ -836,7 +1471,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr lang="zh-CN" sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -852,9 +1487,11 @@
               <a:rPr lang="en-US"/>
               <a:t>'col-3'</a:t>
             </a:r>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -863,26 +1500,6 @@
         </a:ln>
         <a:effectLst/>
       </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="zh-CN"/>
-        </a:p>
-      </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
@@ -891,10 +1508,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.10870603674540683"/>
-          <c:y val="0.17820610965296008"/>
-          <c:w val="0.83773840769903762"/>
-          <c:h val="0.62308654126567509"/>
+          <c:x val="0.108706036745407"/>
+          <c:y val="0.17820610965296"/>
+          <c:w val="0.837738407699038"/>
+          <c:h val="0.623086541265675"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -926,6 +1543,9 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
           <c:cat>
             <c:numRef>
               <c:f>Sheet2!$G$6:$G$9</c:f>
@@ -969,11 +1589,6 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-23F6-C44D-8972-873DF2C709FB}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -983,6 +1598,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
+        <c:marker val="0"/>
         <c:smooth val="0"/>
         <c:axId val="280908351"/>
         <c:axId val="280933119"/>
@@ -1001,7 +1617,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1017,9 +1633,11 @@
                   <a:rPr lang="en-US"/>
                   <a:t>col-1</a:t>
                 </a:r>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1028,26 +1646,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="zh-CN"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -1071,7 +1669,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1083,7 +1681,6 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="280933119"/>
@@ -1121,7 +1718,7 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr lang="zh-CN" sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
                         <a:lumMod val="65000"/>
@@ -1137,9 +1734,11 @@
                   <a:rPr lang="en-US"/>
                   <a:t>col-3</a:t>
                 </a:r>
+                <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1148,26 +1747,6 @@
             </a:ln>
             <a:effectLst/>
           </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="zh-CN"/>
-            </a:p>
-          </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
@@ -1185,7 +1764,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="zh-CN" sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -1197,7 +1776,6 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="280908351"/>
@@ -1214,13 +1792,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
@@ -1243,9 +1814,8 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr lang="zh-CN"/>
       </a:pPr>
-      <a:endParaRPr lang="zh-CN"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2369,7 +2939,534 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>271780</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>100965</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1941195" cy="510540"/>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:sp>
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="文本框 2"/>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2176780" y="1367790"/>
+              <a:ext cx="1941195" cy="510540"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a14:m>
+                <m:oMathPara xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                  <m:oMathParaPr>
+                    <m:jc m:val="centerGroup"/>
+                  </m:oMathParaPr>
+                  <m:oMath xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math">
+                    <m:sSup>
+                      <m:sSupPr>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                            <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                            <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:sSupPr>
+                      <m:e>
+                        <m:d>
+                          <m:dPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                                <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                                <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:dPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                                <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                                <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑥</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                                <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                                <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                              </a:rPr>
+                              <m:t>+</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                                <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                                <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑎</m:t>
+                            </m:r>
+                          </m:e>
+                        </m:d>
+                      </m:e>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                            <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                            <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑛</m:t>
+                        </m:r>
+                      </m:sup>
+                    </m:sSup>
+                    <m:r>
+                      <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                        <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                        <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                      </a:rPr>
+                      <m:t>=</m:t>
+                    </m:r>
+                    <m:nary>
+                      <m:naryPr>
+                        <m:chr m:val="∑"/>
+                        <m:limLoc m:val="undOvr"/>
+                        <m:ctrlPr>
+                          <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                            <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                            <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                          </a:rPr>
+                        </m:ctrlPr>
+                      </m:naryPr>
+                      <m:sub>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                            <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                            <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑘</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                            <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                            <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                          </a:rPr>
+                          <m:t>=</m:t>
+                        </m:r>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                            <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                            <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                          </a:rPr>
+                          <m:t>0</m:t>
+                        </m:r>
+                      </m:sub>
+                      <m:sup>
+                        <m:r>
+                          <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                            <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                            <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                          </a:rPr>
+                          <m:t>𝑛</m:t>
+                        </m:r>
+                      </m:sup>
+                      <m:e>
+                        <m:d>
+                          <m:dPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                                <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                                <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:dPr>
+                          <m:e>
+                            <m:f>
+                              <m:fPr>
+                                <m:type m:val="noBar"/>
+                                <m:ctrlPr>
+                                  <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                                    <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                                    <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                                  </a:rPr>
+                                </m:ctrlPr>
+                              </m:fPr>
+                              <m:num>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                                    <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                                    <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑛</m:t>
+                                </m:r>
+                              </m:num>
+                              <m:den>
+                                <m:r>
+                                  <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                                    <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                                    <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                                  </a:rPr>
+                                  <m:t>𝑘</m:t>
+                                </m:r>
+                              </m:den>
+                            </m:f>
+                          </m:e>
+                        </m:d>
+                        <m:sSup>
+                          <m:sSupPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                                <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                                <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSupPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                                <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                                <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑥</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sup>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                                <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                                <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑘</m:t>
+                            </m:r>
+                          </m:sup>
+                        </m:sSup>
+                        <m:sSup>
+                          <m:sSupPr>
+                            <m:ctrlPr>
+                              <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                                <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                                <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                              </a:rPr>
+                            </m:ctrlPr>
+                          </m:sSupPr>
+                          <m:e>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                                <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                                <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑎</m:t>
+                            </m:r>
+                          </m:e>
+                          <m:sup>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                                <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                                <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑛</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                                <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                                <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                              </a:rPr>
+                              <m:t>−</m:t>
+                            </m:r>
+                            <m:r>
+                              <a:rPr lang="en-US" altLang="zh-CN" sz="1100" i="1">
+                                <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                                <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                              </a:rPr>
+                              <m:t>𝑘</m:t>
+                            </m:r>
+                          </m:sup>
+                        </m:sSup>
+                      </m:e>
+                    </m:nary>
+                  </m:oMath>
+                </m:oMathPara>
+              </a14:m>
+              <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp>
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="3" name="文本框 2"/>
+            <xdr:cNvSpPr txBox="1"/>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="2176780" y="1367790"/>
+              <a:ext cx="1941195" cy="510540"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+          <xdr:style>
+            <a:lnRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:lnRef>
+            <a:fillRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:fillRef>
+            <a:effectRef idx="0">
+              <a:scrgbClr r="0" g="0" b="0"/>
+            </a:effectRef>
+            <a:fontRef idx="minor">
+              <a:schemeClr val="tx1"/>
+            </a:fontRef>
+          </xdr:style>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:p>
+              <a:pPr algn="l"/>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>𝑥</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>+</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>𝑎</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>)</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>^</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>𝑛</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>=</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>∑</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>_</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>𝑘</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>=</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>0</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>^</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>𝑛</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>▒</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>(</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>𝑛</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>¦</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>𝑘</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>)</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>𝑥</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>^</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>𝑘</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>𝑎</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>^</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>𝑛</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>−</a:t>
+              </a:r>
+              <a:r>
+                <a:rPr lang="en-US" altLang="zh-CN" sz="1100">
+                  <a:latin typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                  <a:cs typeface="DejaVu Math TeX Gyre" panose="02000503000000000000" charset="0"/>
+                </a:rPr>
+                <a:t>𝑘</a:t>
+              </a:r>
+              <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -2383,20 +3480,14 @@
       <xdr:row>35</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
+    <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1" descr="Chart type: Scatter. 'col-2', 'col-3', 'col-4' by 'col-1'&#10;&#10;Description automatically generated">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34996955-0197-0455-BDA6-C6A31120255E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Chart 1" descr="Chart type: Scatter. 'col-2', 'col-3', 'col-4' by 'col-1'&#10;&#10;Description automatically generated"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="3898900" y="3981450"/>
+        <a:ext cx="5159375" cy="2441575"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2419,20 +3510,14 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
+    <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 2" descr="Chart type: Line. 'col-3'&#10;&#10;Description automatically generated">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBC31379-7937-AA65-DF69-07DB3CAB6782}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="3" name="Chart 2" descr="Chart type: Line. 'col-3'&#10;&#10;Description automatically generated"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="9096375" y="889000"/>
+        <a:ext cx="5276850" cy="2432050"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2445,8 +3530,8 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
@@ -2457,32 +3542,26 @@
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CAC53083-F9CE-6543-CEEF-483A9D1A5B16}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="2" name="Picture 1"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6766530" y="3784600"/>
-          <a:ext cx="3444270" cy="3517900"/>
+          <a:off x="7705725" y="3384550"/>
+          <a:ext cx="3914775" cy="3517900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2537,7 +3616,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -2570,26 +3649,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -2622,23 +3684,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2800,28 +3845,26 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82CA3C78-F31C-9C4D-A4A6-F45E1637402D}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="2" width="11.1111111111111"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
@@ -2891,18 +3934,36 @@
         <v>-6</v>
       </c>
     </row>
+    <row r="8" ht="39.3" spans="1:2">
+      <c r="A8">
+        <f>SUM(A2:A7)</f>
+        <v>21</v>
+      </c>
+      <c r="B8" t="str">
+        <f>_xlfn.DISPIMG("ID_EEE2D862C4E9461295D42240896EFDB1",1)</f>
+        <v>=DISPIMG("ID_EEE2D862C4E9461295D42240896EFDB1",1)</v>
+      </c>
+    </row>
+    <row r="9" ht="75" spans="1:1">
+      <c r="A9" t="str">
+        <f>_xlfn.DISPIMG("ID_D0725FD5BF544D4B9C79E66BEBA01A89",1)</f>
+        <v>=DISPIMG("ID_D0725FD5BF544D4B9C79E66BEBA01A89",1)</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{658ABF38-A604-D44B-9FDC-D737B2953C41}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -2916,7 +3977,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2930,7 +3991,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2944,7 +4005,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -3073,7 +4134,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="3:5">
       <c r="C14" t="s">
         <v>3</v>
       </c>
@@ -3084,7 +4145,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="3:5">
       <c r="C15">
         <v>1</v>
       </c>
@@ -3095,7 +4156,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="3:5">
       <c r="C16">
         <v>2</v>
       </c>
@@ -3129,18 +4190,19 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AC60911-27E8-3D4F-B8AE-11B52351794B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelCol="6"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3149,7 +4211,7 @@
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:3">
       <c r="A2" s="1"/>
       <c r="B2" t="s">
         <v>1</v>
@@ -3158,7 +4220,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3169,7 +4231,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -3180,7 +4242,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:3">
       <c r="A5" s="1"/>
       <c r="B5">
         <v>6</v>
@@ -3189,7 +4251,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>8</v>
       </c>
@@ -3205,14 +4267,14 @@
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
       <c r="E7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="5:7">
       <c r="E8" s="1"/>
       <c r="F8" t="s">
         <v>1</v>
@@ -3221,7 +4283,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="5:7">
       <c r="E9">
         <v>1</v>
       </c>
@@ -3232,7 +4294,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="5:7">
       <c r="E10" s="1">
         <v>3</v>
       </c>
@@ -3243,7 +4305,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="5:7">
       <c r="E11" s="1"/>
       <c r="F11">
         <v>6</v>
@@ -3252,7 +4314,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="5:7">
       <c r="E12">
         <v>8</v>
       </c>
@@ -3261,7 +4323,7 @@
       </c>
       <c r="G12" s="1"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="5:7">
       <c r="E13">
         <v>10</v>
       </c>
@@ -3270,29 +4332,30 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="E7:E8"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="F12:G13"/>
     <mergeCell ref="B6:C7"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:G7"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4933F67A-3FE8-2F4D-BB74-9586CAFC801B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25" outlineLevelRow="1"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:1">
@@ -3301,7 +4364,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/mineru/model/xlsx/test_xlsx/xlsx_01.xlsx
+++ b/mineru/model/xlsx/test_xlsx/xlsx_01.xlsx
@@ -34,34 +34,11 @@
   <etc:cellImage>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="ID_EEE2D862C4E9461295D42240896EFDB1" descr="截图 2026-01-14 15-36-42"/>
+        <xdr:cNvPr id="4" name="ID_D0725FD5BF544D4B9C79E66BEBA01A89" descr="20250807-172515"/>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="10058400" cy="5272405"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="ID_D0725FD5BF544D4B9C79E66BEBA01A89" descr="20250807-172515"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2942,12 +2919,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>271780</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>923925</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>100965</xdr:rowOff>
+      <xdr:rowOff>458470</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1941195" cy="510540"/>
+    <xdr:ext cx="1941830" cy="510540"/>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
         <xdr:sp>
@@ -2957,8 +2934,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2176780" y="1367790"/>
-              <a:ext cx="1941195" cy="510540"/>
+              <a:off x="1876425" y="1447800"/>
+              <a:ext cx="1941830" cy="510540"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -3224,8 +3201,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="2176780" y="1367790"/>
-              <a:ext cx="1941195" cy="510540"/>
+              <a:off x="1876425" y="1447800"/>
+              <a:ext cx="1941830" cy="510540"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -3934,14 +3911,10 @@
         <v>-6</v>
       </c>
     </row>
-    <row r="8" ht="39.3" spans="1:2">
+    <row r="8" spans="1:1">
       <c r="A8">
         <f>SUM(A2:A7)</f>
         <v>21</v>
-      </c>
-      <c r="B8" t="str">
-        <f>_xlfn.DISPIMG("ID_EEE2D862C4E9461295D42240896EFDB1",1)</f>
-        <v>=DISPIMG("ID_EEE2D862C4E9461295D42240896EFDB1",1)</v>
       </c>
     </row>
     <row r="9" ht="75" spans="1:1">
